--- a/reports/Debug-purgatory-20260104/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Week Ending (Prior Year)_Visits.xlsx
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C2" s="2">
-        <v>2793</v>
+        <v>2869</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,10 +462,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C4" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45658</v>
+        <v>45657</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -490,10 +490,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C6" s="2">
-        <v>26</v>
+        <v>2027</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -507,7 +507,7 @@
         <v>45660</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C9" s="2">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45660</v>
+        <v>45657</v>
       </c>
       <c r="C10" s="2">
-        <v>1871</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45660</v>
+        <v>45657</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45660</v>
+        <v>45657</v>
       </c>
       <c r="C12" s="2">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45660</v>
+        <v>45657</v>
       </c>
       <c r="C13" s="2">
-        <v>179</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
@@ -602,13 +602,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C14" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45656</v>
+        <v>45658</v>
       </c>
       <c r="C15" s="2">
-        <v>-3</v>
+        <v>380</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -633,10 +633,10 @@
         <v>45658</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>684</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,10 +647,10 @@
         <v>45658</v>
       </c>
       <c r="C17" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,7 +661,7 @@
         <v>45659</v>
       </c>
       <c r="C18" s="2">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>6</v>
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C19" s="2">
-        <v>311</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C20" s="2">
-        <v>2084</v>
+        <v>487</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C21" s="2">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>6</v>
@@ -714,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45661</v>
+        <v>45656</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45662</v>
+        <v>45657</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>851</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45662</v>
+        <v>45657</v>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C25" s="2">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C26" s="2">
-        <v>1125</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45656</v>
+        <v>45660</v>
       </c>
       <c r="C27" s="2">
-        <v>10</v>
+        <v>672</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45656</v>
+        <v>45660</v>
       </c>
       <c r="C28" s="2">
-        <v>808</v>
+        <v>26</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45657</v>
+        <v>45661</v>
       </c>
       <c r="C29" s="2">
-        <v>313</v>
+        <v>1965</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C30" s="2">
-        <v>2335</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +840,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45659</v>
+        <v>45656</v>
       </c>
       <c r="C31" s="2">
-        <v>38</v>
+        <v>-3</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +854,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C32" s="2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C33" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>6</v>
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C34" s="2">
-        <v>303</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C35" s="2">
-        <v>1656</v>
+        <v>311</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C36" s="2">
-        <v>18</v>
+        <v>2084</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C37" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>6</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
       <c r="C38" s="2">
-        <v>2869</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,7 +952,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45656</v>
+        <v>45662</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45656</v>
+        <v>45662</v>
       </c>
       <c r="C40" s="2">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>6</v>
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45657</v>
+        <v>45662</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C42" s="2">
-        <v>2027</v>
+        <v>1125</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C43" s="2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>6</v>
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45661</v>
+        <v>45656</v>
       </c>
       <c r="C44" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>6</v>
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C45" s="2">
-        <v>63</v>
+        <v>1383</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>6</v>
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>6</v>
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C47" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>6</v>
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>6</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C49" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>6</v>
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>1733</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>6</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C51" s="2">
-        <v>380</v>
+        <v>101</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C52" s="2">
-        <v>684</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C53" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C54" s="2">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>6</v>
@@ -1176,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>1215</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>6</v>
@@ -1190,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45661</v>
+        <v>45657</v>
       </c>
       <c r="C56" s="2">
-        <v>487</v>
+        <v>95</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C57" s="2">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>6</v>
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45656</v>
+        <v>45659</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>712</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,13 +1232,13 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C59" s="2">
-        <v>851</v>
+        <v>1567</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C60" s="2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C61" s="2">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>6</v>
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>6</v>
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C63" s="2">
-        <v>672</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C64" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C65" s="2">
-        <v>1965</v>
+        <v>288</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1333,7 +1333,7 @@
         <v>45662</v>
       </c>
       <c r="C66" s="2">
-        <v>2</v>
+        <v>2295</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>6</v>
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45656</v>
+        <v>45662</v>
       </c>
       <c r="C67" s="2">
-        <v>1215</v>
+        <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>6</v>
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45657</v>
+        <v>45662</v>
       </c>
       <c r="C68" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>6</v>
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45658</v>
+        <v>45657</v>
       </c>
       <c r="C69" s="2">
-        <v>12</v>
+        <v>2793</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45659</v>
+        <v>45657</v>
       </c>
       <c r="C70" s="2">
-        <v>712</v>
+        <v>3</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45659</v>
+        <v>45657</v>
       </c>
       <c r="C71" s="2">
-        <v>1567</v>
+        <v>122</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>6</v>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C72" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>6</v>
@@ -1431,7 +1431,7 @@
         <v>45659</v>
       </c>
       <c r="C73" s="2">
-        <v>175</v>
+        <v>26</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>6</v>
@@ -1445,7 +1445,7 @@
         <v>45660</v>
       </c>
       <c r="C74" s="2">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>6</v>
@@ -1456,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C76" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>6</v>
@@ -1484,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C77" s="2">
-        <v>288</v>
+        <v>1871</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C78" s="2">
-        <v>2295</v>
+        <v>2</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>6</v>
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C79" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>6</v>
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C80" s="2">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>6</v>
@@ -1540,13 +1540,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
       <c r="C81" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1557,7 +1557,7 @@
         <v>45656</v>
       </c>
       <c r="C82" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>6</v>
@@ -1568,13 +1568,13 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C83" s="2">
-        <v>1383</v>
+        <v>808</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1582,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45658</v>
+        <v>45657</v>
       </c>
       <c r="C84" s="2">
-        <v>4</v>
+        <v>313</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1599,10 +1599,10 @@
         <v>45658</v>
       </c>
       <c r="C85" s="2">
-        <v>2</v>
+        <v>2335</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C86" s="2">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>6</v>
@@ -1627,10 +1627,10 @@
         <v>45659</v>
       </c>
       <c r="C87" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1641,7 +1641,7 @@
         <v>45660</v>
       </c>
       <c r="C88" s="2">
-        <v>1733</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>6</v>
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C89" s="2">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1669,10 +1669,10 @@
         <v>45661</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>1656</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C91" s="2">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>6</v>
@@ -1697,7 +1697,7 @@
         <v>45662</v>
       </c>
       <c r="C92" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>6</v>
